--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62526490</v>
+        <v>121115001</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,27 +710,28 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557792.2317554107</v>
+        <v>557898</v>
       </c>
       <c r="R2" t="n">
-        <v>6598618.88395116</v>
+        <v>6598639</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,33 +769,42 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tall</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Henrik Berg, Christina Munkert</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78505618</v>
+        <v>62526535</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,25 +829,26 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Köping, Vstm</t>
+          <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557812.1151603226</v>
+        <v>557792</v>
       </c>
       <c r="R3" t="n">
-        <v>6598615.129755657</v>
+        <v>6598619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,27 +875,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,39 +894,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsmark med liten våtmark/mosse</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62526535</v>
+        <v>78505618</v>
       </c>
       <c r="B4" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219788</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,26 +940,25 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållestaskogen, Köping, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557792.2317554107</v>
+        <v>557812</v>
       </c>
       <c r="R4" t="n">
-        <v>6598618.88395116</v>
+        <v>6598615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,27 +985,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,18 +1004,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogsmark med liten våtmark/mosse</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Per Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Per Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1066,12 +1031,7 @@
         <v>62526536</v>
       </c>
       <c r="B5" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557813.9751719102</v>
+        <v>557814</v>
       </c>
       <c r="R5" t="n">
-        <v>6598791.754456714</v>
+        <v>6598792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,19 +1101,9 @@
           <t>2016-09-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,137 +1132,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>121115001</v>
-      </c>
-      <c r="B6" t="n">
-        <v>90733</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ållestaskogen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>557898</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6598639</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tall</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Henrik Berg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Henrik Berg, Christina Munkert</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121115001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62526535</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62526536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121115001</v>
+        <v>135675836</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557898</v>
+        <v>557772</v>
       </c>
       <c r="R2" t="n">
-        <v>6598639</v>
+        <v>6598631</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,43 +766,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tall</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Berg, Christina Munkert</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121115001</t>
+          <t>https://artportalen.se/Sighting/135675836</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62526535</v>
+        <v>135678201</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>96854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,43 +797,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219788</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557792</v>
+        <v>557933</v>
       </c>
       <c r="R3" t="n">
-        <v>6598619</v>
+        <v>6598578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,17 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,33 +869,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62526535</t>
+          <t>https://artportalen.se/Sighting/135678201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78505618</v>
+        <v>135678202</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>96854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,42 +904,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Köping, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557812</v>
+        <v>557951</v>
       </c>
       <c r="R4" t="n">
-        <v>6598615</v>
+        <v>6598567</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,17 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,35 +980,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsmark med liten våtmark/mosse</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78505618</t>
+          <t>https://artportalen.se/Sighting/135678202</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62526536</v>
+        <v>135678203</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>96854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,39 +1011,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557814</v>
+        <v>557989</v>
       </c>
       <c r="R5" t="n">
-        <v>6598792</v>
+        <v>6598549</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,17 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,22 +1083,1389 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678203</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135678208</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96854</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558027</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6598484</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678208</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121115001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557898</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6598639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Berg, Christina Munkert</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121115001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135675835</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557736</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6598620</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675835</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135678200</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557917</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6598673</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135678207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558017</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6598499</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135678210</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557761</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6598502</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678210</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135678204</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558002</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6598553</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678204</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135678205</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558004</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6598530</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62526535</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557792</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6598619</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-09-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62526535</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>78505618</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Köping, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557812</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6598615</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Skogsmark med liten våtmark/mosse</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Jonsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Jonsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505618</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135678206</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558006</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6598514</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678206</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>62526536</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6598792</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2016-09-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62526536</t>
         </is>
@@ -1164,6 +2477,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135675836</v>
+        <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>92043</v>
+        <v>96854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ållesta, Vstm</t>
+          <t>Ållundaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557772</v>
+        <v>557700</v>
       </c>
       <c r="R2" t="n">
-        <v>6598631</v>
+        <v>6598611</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,68 +765,71 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett stort antal tätt liggande mindre plantor samt ytterligare utspridda i närheten.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Bertil Svensson, Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135675836</t>
+          <t>https://artportalen.se/Sighting/135711885</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135678201</v>
+        <v>135675836</v>
       </c>
       <c r="B3" t="n">
-        <v>96854</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557933</v>
+        <v>557772</v>
       </c>
       <c r="R3" t="n">
-        <v>6598578</v>
+        <v>6598631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,13 +899,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678201</t>
+          <t>https://artportalen.se/Sighting/135675836</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135678202</v>
+        <v>135678201</v>
       </c>
       <c r="B4" t="n">
         <v>96854</v>
@@ -932,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557951</v>
+        <v>557933</v>
       </c>
       <c r="R4" t="n">
-        <v>6598567</v>
+        <v>6598578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,13 +1006,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678202</t>
+          <t>https://artportalen.se/Sighting/135678201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135678203</v>
+        <v>135678202</v>
       </c>
       <c r="B5" t="n">
         <v>96854</v>
@@ -1039,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557989</v>
+        <v>557951</v>
       </c>
       <c r="R5" t="n">
-        <v>6598549</v>
+        <v>6598567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,13 +1113,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678203</t>
+          <t>https://artportalen.se/Sighting/135678202</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135678208</v>
+        <v>135678203</v>
       </c>
       <c r="B6" t="n">
         <v>96854</v>
@@ -1146,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558027</v>
+        <v>557989</v>
       </c>
       <c r="R6" t="n">
-        <v>6598484</v>
+        <v>6598549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,69 +1220,58 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678208</t>
+          <t>https://artportalen.se/Sighting/135678203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121115001</v>
+        <v>135678208</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>96854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557898</v>
+        <v>558027</v>
       </c>
       <c r="R7" t="n">
-        <v>6598639</v>
+        <v>6598484</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,12 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,89 +1313,83 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tall</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Berg, Christina Munkert</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121115001</t>
+          <t>https://artportalen.se/Sighting/135678208</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135675835</v>
+        <v>121115001</v>
       </c>
       <c r="B8" t="n">
-        <v>57977</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ållesta, Vstm</t>
+          <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557736</v>
+        <v>557898</v>
       </c>
       <c r="R8" t="n">
-        <v>6598620</v>
+        <v>6598639</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,12 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,30 +1427,44 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tall</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Henrik Berg, Christina Munkert</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135675835</t>
+          <t>https://artportalen.se/Sighting/121115001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135678200</v>
+        <v>135675835</v>
       </c>
       <c r="B9" t="n">
         <v>57977</v>
@@ -1498,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557917</v>
+        <v>557736</v>
       </c>
       <c r="R9" t="n">
-        <v>6598673</v>
+        <v>6598620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,13 +1568,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678200</t>
+          <t>https://artportalen.se/Sighting/135675835</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135678207</v>
+        <v>135678200</v>
       </c>
       <c r="B10" t="n">
         <v>57977</v>
@@ -1598,7 +1607,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1608,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558017</v>
+        <v>557917</v>
       </c>
       <c r="R10" t="n">
-        <v>6598499</v>
+        <v>6598673</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,13 +1678,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678207</t>
+          <t>https://artportalen.se/Sighting/135678200</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135678210</v>
+        <v>135678207</v>
       </c>
       <c r="B11" t="n">
         <v>57977</v>
@@ -1718,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557761</v>
+        <v>558017</v>
       </c>
       <c r="R11" t="n">
-        <v>6598502</v>
+        <v>6598499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,16 +1788,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678210</t>
+          <t>https://artportalen.se/Sighting/135678207</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135678204</v>
+        <v>135678210</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>57977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,30 +1805,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1829,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558002</v>
+        <v>557761</v>
       </c>
       <c r="R12" t="n">
-        <v>6598553</v>
+        <v>6598502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1881,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1891,13 +1898,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678204</t>
+          <t>https://artportalen.se/Sighting/135678210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135678205</v>
+        <v>135678204</v>
       </c>
       <c r="B13" t="n">
         <v>8461</v>
@@ -1941,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558004</v>
+        <v>558002</v>
       </c>
       <c r="R13" t="n">
-        <v>6598530</v>
+        <v>6598553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,16 +2010,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678205</t>
+          <t>https://artportalen.se/Sighting/135678204</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62526535</v>
+        <v>135678205</v>
       </c>
       <c r="B14" t="n">
-        <v>99026</v>
+        <v>8461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,43 +2027,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219788</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557792</v>
+        <v>558004</v>
       </c>
       <c r="R14" t="n">
-        <v>6598619</v>
+        <v>6598530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,17 +2090,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,33 +2104,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62526535</t>
+          <t>https://artportalen.se/Sighting/135678205</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>78505618</v>
+        <v>62526535</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,16 +2139,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2153,25 +2156,26 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Köping, Vstm</t>
+          <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557812</v>
+        <v>557792</v>
       </c>
       <c r="R15" t="n">
-        <v>6598615</v>
+        <v>6598619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,17 +2202,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2016-09-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,86 +2221,76 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Skogsmark med liten våtmark/mosse</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78505618</t>
+          <t>https://artportalen.se/Sighting/62526535</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135678206</v>
+        <v>78505618</v>
       </c>
       <c r="B16" t="n">
-        <v>99269</v>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ållesta, Vstm</t>
+          <t>Ållestaskogen, Köping, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558006</v>
+        <v>557812</v>
       </c>
       <c r="R16" t="n">
-        <v>6598514</v>
+        <v>6598615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,12 +2317,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,70 +2340,82 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Skogsmark med liten våtmark/mosse</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Per Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Per Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135678206</t>
+          <t>https://artportalen.se/Sighting/78505618</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62526536</v>
+        <v>135678206</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557814</v>
+        <v>558006</v>
       </c>
       <c r="R17" t="n">
-        <v>6598792</v>
+        <v>6598514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,17 +2442,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,22 +2456,135 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678206</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>62526536</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557814</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6598792</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2016-09-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62526536</t>
         </is>
@@ -2489,6 +2608,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121115001</v>
+        <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>96859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållundaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557898</v>
+        <v>557700</v>
       </c>
       <c r="R2" t="n">
-        <v>6598639</v>
+        <v>6598611</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,12 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett stort antal tätt liggande mindre plantor samt ytterligare utspridda i närheten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,47 +776,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Berg, Christina Munkert</t>
+          <t>Bertil Svensson, Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121115001</t>
+          <t>https://artportalen.se/Sighting/135711885</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62526535</v>
+        <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>96859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,46 +810,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219788</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557792</v>
+        <v>557636</v>
       </c>
       <c r="R3" t="n">
-        <v>6598619</v>
+        <v>6598742</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,17 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,33 +886,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62526535</t>
+          <t>https://artportalen.se/Sighting/135842557</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78505618</v>
+        <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>96859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,45 +926,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Köping, Vstm</t>
+          <t>Ållestaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557812</v>
+        <v>557667</v>
       </c>
       <c r="R4" t="n">
-        <v>6598615</v>
+        <v>6598721</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,17 +988,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,73 +1008,71 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsmark med liten våtmark/mosse</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Jonsson</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78505618</t>
+          <t>https://artportalen.se/Sighting/135842605</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62526536</v>
+        <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ållestaskogen, Vstm</t>
+          <t>Ållesta, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557814</v>
+        <v>557772</v>
       </c>
       <c r="R5" t="n">
-        <v>6598792</v>
+        <v>6598631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,17 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,22 +1113,1942 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675836</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135678201</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557933</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6598578</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678201</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135678202</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6598567</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678202</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135678203</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557989</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6598549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135678208</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558027</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6598484</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678208</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135842634</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557726</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6598654</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135842634</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135842654</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557769</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6598646</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135842654</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121115001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557898</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6598639</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tall</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Berg, Christina Munkert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121115001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135675835</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557736</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6598620</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675835</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135678200</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557917</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6598673</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135678207</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558017</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6598499</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135678210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>557761</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6598502</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678210</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135678204</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6598553</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678204</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135678205</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558004</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6598530</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678205</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>62526535</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557792</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6598619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2016-09-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62526535</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>78505618</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Köping, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557812</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6598615</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kan vara både Jungfru Marie nycklar och skogsnycklar. Jag ska återkomma dit med stövlar på fötterna.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Skogsmark med liten våtmark/mosse</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505618</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135678206</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ållesta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>558006</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6598514</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135678206</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>62526536</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ållestaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>557814</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6598792</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2016-09-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fynd gjort i samband med naturvärdesinventering på uppdrag av Köpings kommun</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62526536</t>
         </is>
@@ -1164,6 +3060,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135675835</v>
       </c>
       <c r="B13" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>135678200</v>
       </c>
       <c r="B14" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135678207</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135678210</v>
       </c>
       <c r="B16" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>135678204</v>
       </c>
       <c r="B17" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135678205</v>
       </c>
       <c r="B18" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135675835</v>
       </c>
       <c r="B13" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>135678200</v>
       </c>
       <c r="B14" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135678207</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135678210</v>
       </c>
       <c r="B16" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135675835</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>135678200</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135678207</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135678210</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135675836</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135678201</v>
       </c>
       <c r="B6" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135678202</v>
       </c>
       <c r="B7" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135678203</v>
       </c>
       <c r="B8" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135678208</v>
       </c>
       <c r="B9" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135675835</v>
       </c>
       <c r="B13" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>135678200</v>
       </c>
       <c r="B14" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135678207</v>
       </c>
       <c r="B15" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135678210</v>
       </c>
       <c r="B16" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>135678206</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711885</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24621-2026 artfynd.xlsx
+++ b/artfynd/A 24621-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135842557</v>
       </c>
       <c r="B3" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135842605</v>
       </c>
       <c r="B4" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>135842634</v>
       </c>
       <c r="B10" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135842654</v>
       </c>
       <c r="B11" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
